--- a/ds/planejamento/3semestre/planos/Plano_de_Ensino_PSOF2.xlsx
+++ b/ds/planejamento/3semestre/planos/Plano_de_Ensino_PSOF2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESENVOLVIMENTO\Desktop\senai2026\ds\planejamento\3semestre\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D237A9F-42D9-44F4-BD72-68E7C4864F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BA155C-BD22-45F0-AA91-BA65AF7A8EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="h9gkGl1sfnRHyr05LFfZmsKJ7cUyj85gDjaHNauDRX4="/>
@@ -1670,6 +1673,194 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1679,34 +1870,10 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1715,21 +1882,94 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1742,8 +1982,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1789,258 +2027,23 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2448,134 +2451,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="132"/>
-      <c r="C3" s="121" t="s">
+      <c r="B3" s="135"/>
+      <c r="C3" s="139" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="122"/>
-      <c r="E3" s="126" t="s">
+      <c r="D3" s="140"/>
+      <c r="E3" s="143" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="127"/>
-      <c r="G3" s="119" t="s">
+      <c r="F3" s="144"/>
+      <c r="G3" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119" t="s">
+      <c r="H3" s="137"/>
+      <c r="I3" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="119"/>
+      <c r="J3" s="137"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="131"/>
-      <c r="B4" s="132"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="130" t="s">
+      <c r="A4" s="134"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="130"/>
-      <c r="G4" s="133" t="s">
+      <c r="F4" s="133"/>
+      <c r="G4" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="133"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="137"/>
-      <c r="C5" s="125" t="s">
+      <c r="B5" s="118"/>
+      <c r="C5" s="120" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="144" t="s">
+      <c r="D5" s="120"/>
+      <c r="E5" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="145"/>
-      <c r="G5" s="133" t="s">
+      <c r="F5" s="125"/>
+      <c r="G5" s="136" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="137"/>
-      <c r="B6" s="138"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="146" t="s">
+      <c r="A6" s="118"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="147"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="125"/>
-      <c r="J6" s="125"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="120"/>
+      <c r="J6" s="120"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="139" t="s">
+      <c r="B7" s="118"/>
+      <c r="C7" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="139"/>
-      <c r="E7" s="128" t="s">
+      <c r="D7" s="121"/>
+      <c r="E7" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="129"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="120"/>
     </row>
     <row r="8" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="137"/>
-      <c r="B8" s="138"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="140" t="s">
+      <c r="A9" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="140"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
-      <c r="I9" s="140"/>
-      <c r="J9" s="140"/>
+      <c r="B9" s="122"/>
+      <c r="C9" s="122"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="122"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="122"/>
+      <c r="H9" s="122"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
@@ -2596,14 +2599,14 @@
       <c r="F10" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="141" t="s">
+      <c r="G10" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="141"/>
-      <c r="I10" s="141" t="s">
+      <c r="H10" s="123"/>
+      <c r="I10" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="141"/>
+      <c r="J10" s="123"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2638,17 +2641,17 @@
       <c r="E11" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="166" t="s">
+      <c r="F11" s="128" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="142" t="s">
+      <c r="G11" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="143"/>
-      <c r="I11" s="142" t="s">
+      <c r="H11" s="57"/>
+      <c r="I11" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="143"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2683,15 +2686,15 @@
       <c r="E12" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="167"/>
-      <c r="G12" s="142" t="s">
+      <c r="F12" s="129"/>
+      <c r="G12" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="143"/>
-      <c r="I12" s="134" t="s">
+      <c r="H12" s="57"/>
+      <c r="I12" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="135"/>
+      <c r="J12" s="55"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2726,15 +2729,15 @@
       <c r="E13" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="167"/>
-      <c r="G13" s="142" t="s">
+      <c r="F13" s="129"/>
+      <c r="G13" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="143"/>
-      <c r="I13" s="134" t="s">
+      <c r="H13" s="57"/>
+      <c r="I13" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="J13" s="135"/>
+      <c r="J13" s="55"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -2769,15 +2772,15 @@
       <c r="E14" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="168"/>
-      <c r="G14" s="142" t="s">
+      <c r="F14" s="130"/>
+      <c r="G14" s="56" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="143"/>
-      <c r="I14" s="169" t="s">
+      <c r="H14" s="57"/>
+      <c r="I14" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="J14" s="170"/>
+      <c r="J14" s="59"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -2815,14 +2818,14 @@
       <c r="F15" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="G15" s="142" t="s">
+      <c r="G15" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="143"/>
-      <c r="I15" s="134" t="s">
+      <c r="H15" s="57"/>
+      <c r="I15" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="J15" s="135"/>
+      <c r="J15" s="55"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -2853,10 +2856,10 @@
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="162"/>
-      <c r="H16" s="163"/>
-      <c r="I16" s="164"/>
-      <c r="J16" s="165"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="63"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2876,18 +2879,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="156" t="s">
+      <c r="A17" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="157"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
-      <c r="F17" s="157"/>
-      <c r="G17" s="157"/>
-      <c r="H17" s="157"/>
-      <c r="I17" s="157"/>
-      <c r="J17" s="158"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="78"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2907,18 +2910,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="159" t="s">
+      <c r="A18" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="159"/>
-      <c r="C18" s="159"/>
-      <c r="D18" s="159"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="159"/>
-      <c r="G18" s="159"/>
-      <c r="H18" s="159"/>
-      <c r="I18" s="159"/>
-      <c r="J18" s="159"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="79"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2938,18 +2941,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="152" t="s">
+      <c r="A19" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="152"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
-      <c r="H19" s="152"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="152"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="75"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2969,18 +2972,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="159"/>
-      <c r="C20" s="159"/>
-      <c r="D20" s="159"/>
-      <c r="E20" s="159"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="159"/>
-      <c r="H20" s="159"/>
-      <c r="I20" s="159"/>
-      <c r="J20" s="159"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -3000,18 +3003,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="332.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="152" t="s">
+      <c r="A21" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="152"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="152"/>
-      <c r="I21" s="152"/>
-      <c r="J21" s="152"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="O21" s="1"/>
@@ -3027,18 +3030,18 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="18" x14ac:dyDescent="0.2">
-      <c r="A22" s="159" t="s">
+      <c r="A22" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="159"/>
-      <c r="C22" s="159"/>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="159"/>
-      <c r="G22" s="159"/>
-      <c r="H22" s="159"/>
-      <c r="I22" s="159"/>
-      <c r="J22" s="159"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="79"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -3058,18 +3061,18 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="152" t="s">
+      <c r="A23" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="152"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="152"/>
-      <c r="H23" s="152"/>
-      <c r="I23" s="152"/>
-      <c r="J23" s="152"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -3089,18 +3092,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="153" t="s">
+      <c r="A24" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="153"/>
-      <c r="C24" s="153"/>
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="153"/>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153"/>
-      <c r="I24" s="153"/>
-      <c r="J24" s="153"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="83"/>
+      <c r="J24" s="83"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -3120,22 +3123,22 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="149" t="s">
+      <c r="A25" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="150"/>
-      <c r="C25" s="150"/>
-      <c r="D25" s="151" t="s">
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="151"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="154" t="s">
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="155"/>
-      <c r="I25" s="155"/>
-      <c r="J25" s="155"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="84"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -3155,12 +3158,12 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="150"/>
-      <c r="B26" s="150"/>
-      <c r="C26" s="150"/>
-      <c r="D26" s="151"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="151"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
       <c r="G26" s="24">
         <v>1</v>
       </c>
@@ -3192,18 +3195,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="44" t="s">
+      <c r="C27" s="109"/>
+      <c r="D27" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="45"/>
-      <c r="F27" s="46"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="100"/>
       <c r="G27" s="10"/>
       <c r="H27" s="21"/>
       <c r="I27" s="22"/>
@@ -3227,16 +3230,16 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="88"/>
-      <c r="B28" s="42" t="s">
+      <c r="A28" s="106"/>
+      <c r="B28" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="43"/>
-      <c r="D28" s="44" t="s">
+      <c r="C28" s="109"/>
+      <c r="D28" s="110" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="46"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="100"/>
       <c r="G28" s="10"/>
       <c r="H28" s="21"/>
       <c r="I28" s="17"/>
@@ -3260,16 +3263,16 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="88"/>
-      <c r="B29" s="59" t="s">
+      <c r="A29" s="106"/>
+      <c r="B29" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="44" t="s">
+      <c r="C29" s="112"/>
+      <c r="D29" s="110" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="55"/>
-      <c r="F29" s="56"/>
+      <c r="E29" s="113"/>
+      <c r="F29" s="114"/>
       <c r="G29" s="10"/>
       <c r="H29" s="21"/>
       <c r="I29" s="17"/>
@@ -3293,16 +3296,16 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="88"/>
-      <c r="B30" s="53" t="s">
+      <c r="A30" s="106"/>
+      <c r="B30" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="44" t="s">
+      <c r="C30" s="116"/>
+      <c r="D30" s="110" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="56"/>
+      <c r="E30" s="113"/>
+      <c r="F30" s="114"/>
       <c r="G30" s="10"/>
       <c r="H30" s="21"/>
       <c r="I30" s="17"/>
@@ -3326,16 +3329,16 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="88"/>
-      <c r="B31" s="98" t="s">
+      <c r="A31" s="106"/>
+      <c r="B31" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="99"/>
-      <c r="D31" s="100" t="s">
+      <c r="C31" s="45"/>
+      <c r="D31" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="101"/>
-      <c r="F31" s="102"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="48"/>
       <c r="G31" s="10"/>
       <c r="H31" s="21"/>
       <c r="I31" s="17"/>
@@ -3359,16 +3362,16 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="88"/>
-      <c r="B32" s="61" t="s">
+      <c r="A32" s="106"/>
+      <c r="B32" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="62"/>
-      <c r="D32" s="95" t="s">
+      <c r="C32" s="53"/>
+      <c r="D32" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="E32" s="96"/>
-      <c r="F32" s="97"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="51"/>
       <c r="G32" s="10"/>
       <c r="H32" s="21"/>
       <c r="I32" s="17"/>
@@ -3392,16 +3395,16 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="88"/>
-      <c r="B33" s="61" t="s">
+      <c r="A33" s="106"/>
+      <c r="B33" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="62"/>
-      <c r="D33" s="95" t="s">
+      <c r="C33" s="53"/>
+      <c r="D33" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="96"/>
-      <c r="F33" s="97"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="51"/>
       <c r="G33" s="10"/>
       <c r="H33" s="21"/>
       <c r="I33" s="17"/>
@@ -3425,16 +3428,16 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="89"/>
-      <c r="B34" s="61" t="s">
+      <c r="A34" s="107"/>
+      <c r="B34" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="94" t="s">
+      <c r="C34" s="53"/>
+      <c r="D34" s="98" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="45"/>
-      <c r="F34" s="46"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="100"/>
       <c r="G34" s="10"/>
       <c r="H34" s="21"/>
       <c r="I34" s="17"/>
@@ -3458,18 +3461,18 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="90" t="s">
+      <c r="A35" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="92" t="s">
+      <c r="B35" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="93"/>
-      <c r="D35" s="94" t="s">
+      <c r="C35" s="104"/>
+      <c r="D35" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="46"/>
+      <c r="E35" s="99"/>
+      <c r="F35" s="100"/>
       <c r="G35" s="10"/>
       <c r="H35" s="21"/>
       <c r="I35" s="17"/>
@@ -3493,16 +3496,16 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="91"/>
-      <c r="B36" s="92" t="s">
+      <c r="A36" s="102"/>
+      <c r="B36" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="93"/>
-      <c r="D36" s="94" t="s">
+      <c r="C36" s="104"/>
+      <c r="D36" s="98" t="s">
         <v>105</v>
       </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="46"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="100"/>
       <c r="G36" s="10"/>
       <c r="H36" s="21"/>
       <c r="I36" s="17"/>
@@ -3526,16 +3529,16 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="91"/>
-      <c r="B37" s="92" t="s">
+      <c r="A37" s="102"/>
+      <c r="B37" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="93"/>
-      <c r="D37" s="94" t="s">
+      <c r="C37" s="104"/>
+      <c r="D37" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="E37" s="45"/>
-      <c r="F37" s="46"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="100"/>
       <c r="G37" s="10"/>
       <c r="H37" s="21"/>
       <c r="I37" s="17"/>
@@ -3559,14 +3562,14 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="103"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="103"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
+      <c r="A38" s="97"/>
+      <c r="B38" s="97"/>
+      <c r="C38" s="97"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="97"/>
+      <c r="G38" s="97"/>
+      <c r="H38" s="97"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -3588,18 +3591,18 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="104" t="s">
+      <c r="A39" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B39" s="105"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="105"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="57" t="s">
+      <c r="B39" s="94"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="105"/>
-      <c r="H39" s="58"/>
+      <c r="G39" s="94"/>
+      <c r="H39" s="95"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -3624,17 +3627,17 @@
       <c r="A40" s="11">
         <v>8</v>
       </c>
-      <c r="B40" s="111" t="s">
+      <c r="B40" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="112">
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="68">
         <v>100</v>
       </c>
-      <c r="G40" s="70"/>
-      <c r="H40" s="71"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="67"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -3659,17 +3662,17 @@
       <c r="A41" s="11">
         <v>7</v>
       </c>
-      <c r="B41" s="113" t="s">
+      <c r="B41" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="112">
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="68">
         <v>95</v>
       </c>
-      <c r="G41" s="70"/>
-      <c r="H41" s="71"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="67"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -3694,17 +3697,17 @@
       <c r="A42" s="11">
         <v>6</v>
       </c>
-      <c r="B42" s="113" t="s">
+      <c r="B42" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="112">
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="68">
         <v>90</v>
       </c>
-      <c r="G42" s="70"/>
-      <c r="H42" s="71"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="67"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -3729,17 +3732,17 @@
       <c r="A43" s="11">
         <v>5</v>
       </c>
-      <c r="B43" s="106" t="s">
+      <c r="B43" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="107"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="108"/>
-      <c r="F43" s="109">
+      <c r="C43" s="87"/>
+      <c r="D43" s="87"/>
+      <c r="E43" s="88"/>
+      <c r="F43" s="89">
         <v>80</v>
       </c>
-      <c r="G43" s="148"/>
-      <c r="H43" s="110"/>
+      <c r="G43" s="90"/>
+      <c r="H43" s="91"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -3764,17 +3767,17 @@
       <c r="A44" s="11">
         <v>4</v>
       </c>
-      <c r="B44" s="106" t="s">
+      <c r="B44" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="107"/>
-      <c r="D44" s="107"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="109">
+      <c r="C44" s="87"/>
+      <c r="D44" s="87"/>
+      <c r="E44" s="88"/>
+      <c r="F44" s="89">
         <v>70</v>
       </c>
-      <c r="G44" s="148"/>
-      <c r="H44" s="110"/>
+      <c r="G44" s="90"/>
+      <c r="H44" s="91"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -3799,17 +3802,17 @@
       <c r="A45" s="11">
         <v>3</v>
       </c>
-      <c r="B45" s="113" t="s">
+      <c r="B45" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="71"/>
-      <c r="F45" s="112">
+      <c r="C45" s="66"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="68">
         <v>60</v>
       </c>
-      <c r="G45" s="70"/>
-      <c r="H45" s="71"/>
+      <c r="G45" s="66"/>
+      <c r="H45" s="67"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -3834,17 +3837,17 @@
       <c r="A46" s="11">
         <v>2</v>
       </c>
-      <c r="B46" s="118" t="s">
+      <c r="B46" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="112">
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="68">
         <v>50</v>
       </c>
-      <c r="G46" s="70"/>
-      <c r="H46" s="71"/>
+      <c r="G46" s="66"/>
+      <c r="H46" s="67"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -3869,17 +3872,17 @@
       <c r="A47" s="11">
         <v>1</v>
       </c>
-      <c r="B47" s="111" t="s">
+      <c r="B47" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="71"/>
-      <c r="F47" s="112">
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="68">
         <v>30</v>
       </c>
-      <c r="G47" s="70"/>
-      <c r="H47" s="71"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="67"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3971,16 +3974,16 @@
       <c r="D50" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E50" s="114">
+      <c r="E50" s="69">
         <v>1</v>
       </c>
-      <c r="F50" s="114">
+      <c r="F50" s="69">
         <v>0</v>
       </c>
-      <c r="G50" s="154" t="s">
+      <c r="G50" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="H50" s="116" t="s">
+      <c r="H50" s="73" t="s">
         <v>99</v>
       </c>
       <c r="I50" s="1"/>
@@ -4010,10 +4013,10 @@
       <c r="D51" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="115"/>
-      <c r="F51" s="115"/>
-      <c r="G51" s="161"/>
-      <c r="H51" s="117"/>
+      <c r="E51" s="70"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="72"/>
+      <c r="H51" s="74"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -4035,18 +4038,18 @@
       <c r="AA51" s="1"/>
     </row>
     <row r="52" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="160" t="s">
+      <c r="A52" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="160"/>
-      <c r="C52" s="160"/>
-      <c r="D52" s="160"/>
-      <c r="E52" s="160"/>
-      <c r="F52" s="160"/>
-      <c r="G52" s="160"/>
-      <c r="H52" s="160"/>
-      <c r="I52" s="160"/>
-      <c r="J52" s="160"/>
+      <c r="B52" s="64"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="64"/>
+      <c r="I52" s="64"/>
+      <c r="J52" s="64"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -30196,52 +30199,37 @@
     </row>
   </sheetData>
   <mergeCells count="93">
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A25:C26"/>
-    <mergeCell ref="D25:F26"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J8"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="F39:H39"/>
     <mergeCell ref="A38:H38"/>
@@ -30258,45 +30246,63 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J8"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A25:C26"/>
+    <mergeCell ref="D25:F26"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B32:C32"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I14:J14" location="'Projeto 2'!A1" display="Atividade prática de desenvolvimento de uma sprint de um projeto de software que solucione outra parte de um problema cotidiano de uma empresa." xr:uid="{B56A3B22-F41B-4339-9373-1BF0270C2056}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="16" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -30317,15 +30323,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="146" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="148"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -30344,15 +30350,15 @@
       <c r="W1" s="7"/>
     </row>
     <row r="2" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="156"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -30371,15 +30377,15 @@
       <c r="W2" s="7"/>
     </row>
     <row r="3" spans="1:24" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="157" t="s">
         <v>110</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
@@ -30398,13 +30404,13 @@
       <c r="W3" s="7"/>
     </row>
     <row r="4" spans="1:24" ht="398.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="170"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -30423,15 +30429,15 @@
       <c r="W4" s="7"/>
     </row>
     <row r="5" spans="1:24" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -30450,15 +30456,15 @@
       <c r="W5" s="7"/>
     </row>
     <row r="6" spans="1:24" ht="307.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="159" t="s">
         <v>111</v>
       </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
+      <c r="B6" s="159"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="159"/>
+      <c r="E6" s="159"/>
+      <c r="F6" s="159"/>
+      <c r="G6" s="159"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -30477,13 +30483,13 @@
       <c r="W6" s="7"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="78"/>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="159"/>
+      <c r="G7" s="159"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -30502,15 +30508,15 @@
       <c r="W7" s="7"/>
     </row>
     <row r="8" spans="1:24" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
+      <c r="B8" s="161"/>
+      <c r="C8" s="161"/>
+      <c r="D8" s="161"/>
+      <c r="E8" s="161"/>
+      <c r="F8" s="161"/>
+      <c r="G8" s="161"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -30529,15 +30535,15 @@
       <c r="W8" s="8"/>
     </row>
     <row r="9" spans="1:24" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="81" t="s">
+      <c r="A9" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="83"/>
+      <c r="B9" s="163"/>
+      <c r="C9" s="163"/>
+      <c r="D9" s="163"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="163"/>
+      <c r="G9" s="164"/>
       <c r="H9" s="41"/>
       <c r="I9" s="7"/>
       <c r="J9" s="9"/>
@@ -30556,15 +30562,15 @@
       <c r="W9" s="7"/>
     </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="165" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="86"/>
+      <c r="B10" s="166"/>
+      <c r="C10" s="166"/>
+      <c r="D10" s="166"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="167"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
@@ -30583,17 +30589,17 @@
       <c r="W10" s="7"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="66" t="s">
+      <c r="A11" s="149" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="72" t="s">
+      <c r="B11" s="150"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="171" t="s">
+      <c r="E11" s="150"/>
+      <c r="F11" s="150"/>
+      <c r="G11" s="42" t="s">
         <v>115</v>
       </c>
       <c r="H11" s="7"/>
@@ -30614,12 +30620,12 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="69"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
+      <c r="A12" s="152"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
       <c r="G12" s="39" t="s">
         <v>114</v>
       </c>
@@ -30641,19 +30647,19 @@
       <c r="W12" s="7"/>
     </row>
     <row r="13" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="87" t="s">
+      <c r="A13" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="44" t="s">
+      <c r="C13" s="109"/>
+      <c r="D13" s="110" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="173"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="43"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -30673,17 +30679,17 @@
       <c r="X13" s="1"/>
     </row>
     <row r="14" spans="1:24" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
-      <c r="B14" s="42" t="s">
+      <c r="A14" s="106"/>
+      <c r="B14" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="44" t="s">
+      <c r="C14" s="109"/>
+      <c r="D14" s="110" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="173"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="43"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -30703,17 +30709,17 @@
       <c r="X14" s="1"/>
     </row>
     <row r="15" spans="1:24" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="88"/>
-      <c r="B15" s="59" t="s">
+      <c r="A15" s="106"/>
+      <c r="B15" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="44" t="s">
+      <c r="C15" s="112"/>
+      <c r="D15" s="110" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="173"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="43"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -30733,17 +30739,17 @@
       <c r="X15" s="1"/>
     </row>
     <row r="16" spans="1:24" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="88"/>
-      <c r="B16" s="53" t="s">
+      <c r="A16" s="106"/>
+      <c r="B16" s="115" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="44" t="s">
+      <c r="C16" s="116"/>
+      <c r="D16" s="110" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="173"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="43"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -30763,17 +30769,17 @@
       <c r="X16" s="1"/>
     </row>
     <row r="17" spans="1:24" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="88"/>
-      <c r="B17" s="98" t="s">
+      <c r="A17" s="106"/>
+      <c r="B17" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="99"/>
-      <c r="D17" s="100" t="s">
+      <c r="C17" s="45"/>
+      <c r="D17" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="101"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="173"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="43"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -30793,17 +30799,17 @@
       <c r="X17" s="1"/>
     </row>
     <row r="18" spans="1:24" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="88"/>
-      <c r="B18" s="61" t="s">
+      <c r="A18" s="106"/>
+      <c r="B18" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="95" t="s">
+      <c r="C18" s="53"/>
+      <c r="D18" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="96"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="173"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="43"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -30823,17 +30829,17 @@
       <c r="X18" s="1"/>
     </row>
     <row r="19" spans="1:24" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="88"/>
-      <c r="B19" s="61" t="s">
+      <c r="A19" s="106"/>
+      <c r="B19" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="62"/>
-      <c r="D19" s="95" t="s">
+      <c r="C19" s="53"/>
+      <c r="D19" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="96"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="173"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="43"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -30853,17 +30859,17 @@
       <c r="X19" s="1"/>
     </row>
     <row r="20" spans="1:24" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="89"/>
-      <c r="B20" s="61" t="s">
+      <c r="A20" s="107"/>
+      <c r="B20" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="62"/>
-      <c r="D20" s="94" t="s">
+      <c r="C20" s="53"/>
+      <c r="D20" s="98" t="s">
         <v>97</v>
       </c>
-      <c r="E20" s="45"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="173"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="43"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -30883,19 +30889,19 @@
       <c r="X20" s="1"/>
     </row>
     <row r="21" spans="1:24" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="92" t="s">
+      <c r="B21" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94" t="s">
+      <c r="C21" s="104"/>
+      <c r="D21" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="173"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="43"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -30915,17 +30921,17 @@
       <c r="X21" s="1"/>
     </row>
     <row r="22" spans="1:24" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="91"/>
-      <c r="B22" s="92" t="s">
+      <c r="A22" s="102"/>
+      <c r="B22" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="93"/>
-      <c r="D22" s="94" t="s">
+      <c r="C22" s="104"/>
+      <c r="D22" s="98" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="173"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="100"/>
+      <c r="G22" s="43"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -30945,17 +30951,17 @@
       <c r="X22" s="1"/>
     </row>
     <row r="23" spans="1:24" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92" t="s">
+      <c r="A23" s="102"/>
+      <c r="B23" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="93"/>
-      <c r="D23" s="94" t="s">
+      <c r="C23" s="104"/>
+      <c r="D23" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="173"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="43"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -30975,13 +30981,13 @@
       <c r="X23" s="1"/>
     </row>
     <row r="24" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="103"/>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="172"/>
+      <c r="A24" s="97"/>
+      <c r="B24" s="97"/>
+      <c r="C24" s="97"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="97"/>
+      <c r="G24" s="145"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -31001,17 +31007,17 @@
       <c r="X24" s="1"/>
     </row>
     <row r="25" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="57" t="s">
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="58"/>
+      <c r="G25" s="95"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -31034,16 +31040,16 @@
       <c r="A26" s="11">
         <v>8</v>
       </c>
-      <c r="B26" s="111" t="s">
+      <c r="B26" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="112">
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="68">
         <v>100</v>
       </c>
-      <c r="G26" s="71"/>
+      <c r="G26" s="67"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -31066,16 +31072,16 @@
       <c r="A27" s="11">
         <v>7</v>
       </c>
-      <c r="B27" s="113" t="s">
+      <c r="B27" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="112">
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="68">
         <v>95</v>
       </c>
-      <c r="G27" s="71"/>
+      <c r="G27" s="67"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -31098,16 +31104,16 @@
       <c r="A28" s="11">
         <v>6</v>
       </c>
-      <c r="B28" s="113" t="s">
+      <c r="B28" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="112">
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="68">
         <v>90</v>
       </c>
-      <c r="G28" s="71"/>
+      <c r="G28" s="67"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -31130,16 +31136,16 @@
       <c r="A29" s="11">
         <v>5</v>
       </c>
-      <c r="B29" s="106" t="s">
+      <c r="B29" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="109">
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="89">
         <v>80</v>
       </c>
-      <c r="G29" s="110"/>
+      <c r="G29" s="91"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -31162,16 +31168,16 @@
       <c r="A30" s="11">
         <v>4</v>
       </c>
-      <c r="B30" s="106" t="s">
+      <c r="B30" s="86" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="107"/>
-      <c r="D30" s="107"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="109">
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="89">
         <v>70</v>
       </c>
-      <c r="G30" s="110"/>
+      <c r="G30" s="91"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -31194,16 +31200,16 @@
       <c r="A31" s="11">
         <v>3</v>
       </c>
-      <c r="B31" s="113" t="s">
+      <c r="B31" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="112">
+      <c r="C31" s="66"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="68">
         <v>60</v>
       </c>
-      <c r="G31" s="71"/>
+      <c r="G31" s="67"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -31226,16 +31232,16 @@
       <c r="A32" s="11">
         <v>2</v>
       </c>
-      <c r="B32" s="118" t="s">
+      <c r="B32" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="112">
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="68">
         <v>50</v>
       </c>
-      <c r="G32" s="71"/>
+      <c r="G32" s="67"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -31258,16 +31264,16 @@
       <c r="A33" s="11">
         <v>1</v>
       </c>
-      <c r="B33" s="111" t="s">
+      <c r="B33" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="112">
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="68">
         <v>30</v>
       </c>
-      <c r="G33" s="71"/>
+      <c r="G33" s="67"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -31351,13 +31357,13 @@
       <c r="D36" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="114">
+      <c r="E36" s="69">
         <v>1</v>
       </c>
-      <c r="F36" s="114">
+      <c r="F36" s="69">
         <v>0</v>
       </c>
-      <c r="G36" s="116" t="s">
+      <c r="G36" s="73" t="s">
         <v>99</v>
       </c>
       <c r="H36" s="1"/>
@@ -31385,9 +31391,9 @@
       <c r="D37" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E37" s="115"/>
-      <c r="F37" s="115"/>
-      <c r="G37" s="117"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="74"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -31407,15 +31413,15 @@
       <c r="X37" s="1"/>
     </row>
     <row r="38" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="50" t="s">
+      <c r="A38" s="171" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
-      <c r="G38" s="52"/>
+      <c r="B38" s="172"/>
+      <c r="C38" s="172"/>
+      <c r="D38" s="172"/>
+      <c r="E38" s="172"/>
+      <c r="F38" s="172"/>
+      <c r="G38" s="173"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -35996,49 +36002,6 @@
     <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D11:F12"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="A4:G4"/>
@@ -36055,6 +36018,49 @@
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D11:F12"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:G33"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
